--- a/docs/downloads/04/tbl_homeland_alaotra_ambatomanga.xlsx
+++ b/docs/downloads/04/tbl_homeland_alaotra_ambatomanga.xlsx
@@ -397,12 +397,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>5.9</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -465,12 +459,6 @@
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>11.1</v>
       </c>
     </row>
     <row r="6">
